--- a/BaseLineCheck/SecurityCheck_v5检查程序/带服务的批量检查版本/Monitor/summary.xlsx
+++ b/BaseLineCheck/SecurityCheck_v5检查程序/带服务的批量检查版本/Monitor/summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,21 @@
           <t>数据</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Suggestion</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +474,177 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>[{"Issue": "FTP ?????,??? Running", "Suggestion": "????????? FTP ??", "Item": "FTP??"}, {"Issue": "FTP????????", "Suggestion": "????????? FTP ??? ??", "Item": "FTP???"}, {"Issue": "?? 4899 ???", "Suggestion": "?????????&gt;?Windows Defender ????&gt;??????,????????????", "Item": "????"}]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:50:21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FTP ?????,??? Running</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>????????? FTP ??</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FTP??</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:50:21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FTP????????</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>????????? FTP ??? ??</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FTP???</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:50:21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>?? 4899 ???</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>?????????&gt;?Windows Defender ????&gt;??????,????????????</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:56:24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FTP 服务已安装，状态为 Running</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>请在【服务】中禁用 FTP 服务</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FTP服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:56:24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FTP客户端功能已启用</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>请在系统功能中取消 FTP 客户端 勾选</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FTP客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>172.16.1.20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-03-27 10:56:24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>端口 4899 未封禁</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>请进入【控制面板】&gt;【Windows Defender 防火墙】&gt;【高级设置】，添加入站规则封禁该端口。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>端口封禁</t>
         </is>
       </c>
     </row>
